--- a/Cell survival results/2026_3_2/2026_3_2.xlsx
+++ b/Cell survival results/2026_3_2/2026_3_2.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="797" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FEBF9A3-C086-469E-9DB2-46609B7450A3}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell survival results\2026_3_2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E807DF95-5F74-4962-B518-C7636C6F9A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +75,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,9 +170,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -205,7 +210,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -311,7 +316,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -453,7 +458,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -462,13 +467,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -505,7 +510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -522,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -539,7 +544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -556,7 +561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -573,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -590,7 +595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -607,7 +612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -624,7 +629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -641,7 +646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -658,7 +663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -675,7 +680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -695,7 +700,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -712,7 +717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -729,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -746,7 +751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -763,7 +768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -780,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -797,7 +802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -814,7 +819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -831,7 +836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -848,7 +853,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -865,7 +870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -882,7 +887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -899,7 +904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -916,7 +921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -933,7 +938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -950,7 +955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -967,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -984,7 +989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -1001,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -1018,7 +1023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>34</v>
       </c>
@@ -1035,7 +1040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>35</v>
       </c>
@@ -1052,7 +1057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>36</v>
       </c>
@@ -1066,10 +1071,10 @@
         <v>7</v>
       </c>
       <c r="E35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>37</v>
       </c>
@@ -1086,7 +1091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>38</v>
       </c>
@@ -1106,7 +1111,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>39</v>
       </c>
@@ -1123,7 +1128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>40</v>
       </c>
@@ -1140,7 +1145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>41</v>
       </c>
@@ -1157,7 +1162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>43</v>
       </c>
@@ -1174,7 +1179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>44</v>
       </c>
@@ -1191,7 +1196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>45</v>
       </c>
@@ -1208,7 +1213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>46</v>
       </c>
@@ -1225,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>47</v>
       </c>
@@ -1242,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>48</v>
       </c>
@@ -1262,7 +1267,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>49</v>
       </c>
@@ -1279,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>50</v>
       </c>
@@ -1296,7 +1301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>51</v>
       </c>
